--- a/tools/importer/reports/import-ahus-home.report.xlsx
+++ b/tools/importer/reports/import-ahus-home.report.xlsx
@@ -73,7 +73,7 @@
     <t>ahus-home</t>
   </si>
   <si>
-    <t>2026-06-17T22:42:01.096Z</t>
+    <t>2026-06-18T05:28:21.122Z</t>
   </si>
   <si>
     <t>ULTOMIRIS® (ravulizumab-cwvz) | Atypical-HUS Home</t>
